--- a/www/download/COUNTRY.AUT.zdW16.xlsx
+++ b/www/download/COUNTRY.AUT.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Áustria</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>1.0827197921178</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>1.11656989727557</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1.0575296108291</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0.884016973125884</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>0.803923144947343</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.803793907242183</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.796431984708506</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.729660707770887</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>0.67990209409845</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.71694866647548</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.75431847325941</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.718390804597701</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.778331257783313</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.75295534974776</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.752728641324802</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3.756</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3.783</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>3.805</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>3.828</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>3.874</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>3.941</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>4.014</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>4.09</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4.073</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>4.102</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>4.166</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>4.211</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>4.231</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>4.268</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3.245</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3.267</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>3.277</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>3.292</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>3.329</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3.385</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>3.454</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>3.521</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3.497</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>3.527</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>3.592</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>3.643</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>3.665</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>3.697</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>6252.768</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6275.861</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>6246.788</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>6261.408</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>6328.953</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>6364.899</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>6419.74</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>6530.27</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>6670.72</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>6462.196</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>6497.797</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>6597.917</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>6618.083</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>6605.721</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>6656.959</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5384.854</t>
+          <t>7197642659.91335</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5395.217</t>
+          <t>7151589232.35941</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5368.603</t>
+          <t>6848032648.39083</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5374.061</t>
+          <t>7127425462.21803</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5422.009</t>
+          <t>7232693165.3338</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5448.22</t>
+          <t>7040498538.50927</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5489.266</t>
+          <t>7356446214.07595</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5593.98</t>
+          <t>7512835072.31264</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5715.131</t>
+          <t>7720422810.11692</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5497.263</t>
+          <t>7336712674.48228</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>5549.865</t>
+          <t>7677221828.46287</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>5651.305</t>
+          <t>8476624065.91225</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5688.356</t>
+          <t>8475572956.39846</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>5686.141</t>
+          <t>8836487937.85284</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>5729.812</t>
+          <t>8259388356.87435</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2549682660.04977</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2491901332.91315</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2450361444.07766</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2595528636.98474</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2648811113.18915</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2607161605.47632</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2712223411.12113</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2732776698.48403</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2744643680.89551</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2634468229.116</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2555475451.70569</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2641112525.48032</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2719287955.42348</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2964304806.68453</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2959010294.98133</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1365444.97034723</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1322239.92613515</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1138947.30131718</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>974850.936532989</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>840521.735887508</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>773895.973624776</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>739357.903712263</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>637166.326544658</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>566049.112182107</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>630833.551868485</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>673547.359676139</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>639926.592137721</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>668157.241508101</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>682818.774493411</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>631712.226486602</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>28890.406844846</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>28337.2171176753</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>28026.0677491708</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>30731.9343049529</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>34080.4811217751</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>36367.7413585168</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>38396.1275646076</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>43874.7462022208</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>48767.5350701566</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>43019.409151268</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>47602.5776274168</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>51549.6909667337</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>50093.09789657</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>49574.8381960235</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>49804.7645415128</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>65292.2622495001</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>63924.5567610929</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>61661.4656091667</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>69869.7357871344</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>78135.0838456573</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>82149.8411027971</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>90704.3170767123</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>103912.273758827</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>116464.679457349</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>101146.592115722</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>116935.931121601</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>137662.23763856</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>134453.864992367</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>139366.499909021</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>130719.412943404</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.11197027942877</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.16510057149524</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.19094330470124</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.07050730376187</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.04695947287534</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.08971319175461</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.0238989079926</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.04699491294081</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.08228523060425</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.0866689297083</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.17175437795564</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.13974412126656</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.09185496102201</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.918203886178541</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.936394749865562</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.0827197921178</t>
+          <t>785.673285647744</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656989727557</t>
+          <t>762.854183439147</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.0575296108291</t>
+          <t>751.741464875125</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884016973125884</t>
+          <t>792.090062281529</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923144947343</t>
+          <t>804.728187603796</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793907242183</t>
+          <t>783.084267342372</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431984708506</t>
+          <t>801.148280308241</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660707770887</t>
+          <t>791.146053640215</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.67990209409845</t>
+          <t>779.604290480921</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694866647548</t>
+          <t>753.411262301814</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.75431847325941</t>
+          <t>724.53210503497</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.718390804597701</t>
+          <t>735.345919569314</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.778331257783313</t>
+          <t>746.480863790174</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.75295534974776</t>
+          <t>808.827649752665</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.752728641324802</t>
+          <t>800.39879006885</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>2742128806.88207</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>2869565149.15646</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>3315520362.84302</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>3493438449.50694</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3744614484.92093</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>3822571710.00986</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>4204849268.81341</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>4542114445.83309</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>4359029061.84324</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>3821652489.95511</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>3747978478.66724</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>3889856485.98565</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>3833907256.54681</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>4212462069.54502</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>4306038385.09726</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>2225842830.83829</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>2355897530.69026</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>2751976662.34257</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>2843776186.25127</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>3039851201.27986</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>3086179639.59145</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>3502136143.76273</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>3688718095.07775</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>3491550728.96386</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>3126333057.0879</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>3340000213.01773</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>3421879001.76782</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>3334340005.2008</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>3690323703.25851</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>3819229933.16805</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>516285976.043777</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>513667618.466204</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>563543700.50045</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>649662263.255661</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>704763283.641073</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>736392070.418406</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.216</t>
+          <t>702713125.05068</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>853396350.755343</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.592</t>
+          <t>867478332.879376</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>695319432.867216</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.537</t>
+          <t>407978265.649512</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1.675</t>
+          <t>467977484.217829</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1.601</t>
+          <t>499567251.346007</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.709</t>
+          <t>522138366.286511</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.762</t>
+          <t>486808451.929208</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>1659.31862862918</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>1651.65602853163</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>1647.02292933445</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>1640.0282591911</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>1647.24598670539</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>1636.42152372085</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>1621.443129656</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>1619.47194719472</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>1623.35849978413</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>1572.1198723375</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>1573.50577107911</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>1573.45210849579</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>1561.52969822747</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.803</t>
+          <t>1551.49634100422</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1549.88801488807</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>1664.53735561047</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>1658.74914715475</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>1652.61565544821</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>1645.76406441346</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>1653.18903461743</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>1643.05482685135</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>1628.78436086005</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>1626.99915485212</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>1630.84329857207</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>1586.74177761344</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>1583.96311980468</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>1583.75340385596</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>1571.60668524424</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>1561.41463920313</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>1559.5584060534</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>72944.352947751</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>76133.0113642636</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>83959.2651571131</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>100080.993108238</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>118976.47333427</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>135999.243277694</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>151878.965579455</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>180404.449059521</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>203062.723066252</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>160534.761921982</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>179453.875808672</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>208767.806048105</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>199333.573745047</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>206576.539832248</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>210995.335988295</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2140022955.31107</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2214479789.164</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2166780910.69323</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2194553718.0607</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2289351807.58562</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2431904771.31926</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2601924691.74663</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2661559176.60039</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2697013017.81233</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2280316704.36801</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2711345915.53472</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>3121764883.05514</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>3094940630.52584</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>3168384690.05961</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>3039497308.28007</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>69843.3907922765</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>72186.4220182733</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76096.0277985027</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>92698.2566418642</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>110028.287695296</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>125632.549445772</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>139077.077170656</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>161891.477406135</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>183322.985898955</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>147282.61311978</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>164670.78587399</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>196573.989617307</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>187662.601682919</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>193537.604122982</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>194797.260988657</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6252.768</t>
+          <t>4458080024.44369</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6275.861</t>
+          <t>4522323424.26798</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6246.788</t>
+          <t>4356061286.72616</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6261.408</t>
+          <t>4691250638.88492</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6328.953</t>
+          <t>4933126152.24742</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>6364.899</t>
+          <t>5097769405.75161</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6419.74</t>
+          <t>5510405572.97877</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>6530.27</t>
+          <t>5596165667.147</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>6670.72</t>
+          <t>5559596280.01642</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6462.196</t>
+          <t>4973526049.83428</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>6497.797</t>
+          <t>5337176938.12502</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>6597.917</t>
+          <t>6135364275.15834</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>6618.083</t>
+          <t>6084575701.56234</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>6605.721</t>
+          <t>6428212262.63304</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>6656.959</t>
+          <t>6173458061.0905</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5384.854</t>
+          <t>3100.96215547456</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5395.217</t>
+          <t>3946.58934599027</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5368.603</t>
+          <t>7863.23735861039</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5374.061</t>
+          <t>7382.73646637385</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5422.009</t>
+          <t>8948.18563897467</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>5448.22</t>
+          <t>10366.6938319221</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5489.266</t>
+          <t>12801.8884087989</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5593.98</t>
+          <t>18512.9716533858</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5715.131</t>
+          <t>19739.7371672972</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>5497.263</t>
+          <t>13252.1488022021</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>5549.865</t>
+          <t>14783.0899346818</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>5651.305</t>
+          <t>12193.8164307979</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>5688.356</t>
+          <t>11670.9720621276</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>5686.141</t>
+          <t>13038.9357092662</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>5729.812</t>
+          <t>16198.0749996374</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8979.97</t>
+          <t>-2318057069.13262</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8932.45</t>
+          <t>-2307843635.10398</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8588.069</t>
+          <t>-2189280376.03292</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>9029.471</t>
+          <t>-2496696920.82422</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>9141.716</t>
+          <t>-2643774344.6618</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>8889.778</t>
+          <t>-2665864634.43235</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>9303.272</t>
+          <t>-2908480881.23215</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>9441.473</t>
+          <t>-2934606490.54662</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>9743.645</t>
+          <t>-2862583262.20409</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>9416.018</t>
+          <t>-2693209345.46627</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>9746.873</t>
+          <t>-2625831022.5903</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>10752.139</t>
+          <t>-3013599392.10321</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>10728.875</t>
+          <t>-2989635071.0365</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>11134.355</t>
+          <t>-3259827572.57342</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>8259.388</t>
+          <t>-3133960752.81042</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>86225.81824</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>86080.23576</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>91989.8592</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>112597.83808</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>128071.44644</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>130013.30199</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>138989.14424</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>161866.32875</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>177539.82676</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>162440.5002</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>158093.17182</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>173047.3152</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>164579.0256</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>171563.69238</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>174323.77725</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3184.8</t>
+          <t>0.0967839958074399</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3170.239</t>
+          <t>0.0987168355440254</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3112.534</t>
+          <t>0.0996567886961306</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3134.971</t>
+          <t>0.0979945814408869</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3154.712</t>
+          <t>0.100137928913003</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3116.829</t>
+          <t>0.101701051022971</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3114.064</t>
+          <t>0.103553377300122</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>3172.135</t>
+          <t>0.104791208427335</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3232.791</t>
+          <t>0.100431589645877</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3120.432</t>
+          <t>0.0900561689912832</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>3125.263</t>
+          <t>0.0908612752498718</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>3174.199</t>
+          <t>0.0931216382751892</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>3157.72</t>
+          <t>0.090319162102167</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>3143.277</t>
+          <t>0.0881993846436922</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>3146.869</t>
+          <t>0.0865432478066695</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>95449.81144</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>94562.3738</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>101697.48336</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>124410.84656</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>140247.36159</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>144839.86374</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>153227.64824</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>175685.08025</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>198501.66836</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>190005.9326</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>184146.88878</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>200925.3168</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>193159.91552</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>205254.53475</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>210681.7667</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3027.425</t>
+          <t>106568.163656</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2946.77</t>
+          <t>105581.549608</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2900.745</t>
+          <t>113776.180608</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>3078.537</t>
+          <t>139381.079488</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>3121.276</t>
+          <t>157560.683252</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3058.965</t>
+          <t>162871.239531</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>3182.359</t>
+          <t>172554.446128</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>3182.3</t>
+          <t>197800.194615</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3209.638</t>
+          <t>223306.798608</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3123.117</t>
+          <t>214718.873468</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>3003.913</t>
+          <t>208067.063931</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>3114.545</t>
+          <t>226659.12336</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>3196.144</t>
+          <t>217595.629504</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>3455.526</t>
+          <t>231135.046797</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2959.01</t>
+          <t>237169.82482</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>77.87</t>
+          <t>713755.771</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>83.09</t>
+          <t>714189.59256</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>85.08</t>
+          <t>773895.20976</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>74.57</t>
+          <t>959604.53904</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>73.71</t>
+          <t>1099885.73604</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>78.11</t>
+          <t>1148216.46654</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>1215615.418</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>75.78</t>
+          <t>1407231.45575</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>78.06</t>
+          <t>1591984.94812</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>76.02</t>
+          <t>1561523.65204</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>1537288.21593</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>1674537.72</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>77.98</t>
+          <t>1600804.52576</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>1709213.83377</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>93.64</t>
+          <t>1762056.63925</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.799</t>
+          <t>128383.380767281</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>128096.370375164</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>129385.624659274</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>130591.514945293</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.139</t>
+          <t>132409.653289232</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.043</t>
+          <t>134536.78995061</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>138023.44814588</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>141641.264657485</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>145900.661591043</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>143892.48720174</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>144957.939388</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>148111.507557175</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.872</t>
+          <t>150960.230734973</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>152625.861925438</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>153863.041391416</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>115314.932617153</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>115188.29964544</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>116084.075425848</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>116958.224139331</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>118028.826086421</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>119478.874291057</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>122631.743274887</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>125973.238214661</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>129615.555013027</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>126714.680049994</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>128293.02744</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>131294.765552819</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>134207.055339853</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>135625.938148206</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>136611.242629832</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>69080.135548</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>70502.536556</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>77123.911392</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>94036.045152</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>110140.279648</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>116774.821449</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>125881.082032</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>147465.484785</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>159885.579032</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>140624.837892</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>139679.967726</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>155935.69584</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>144583.323456</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>150751.608363</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>152494.10438</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5384854000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5395217000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5368603000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5374061000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>5422009000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>5448220000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5489266000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>5593980000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>5715131000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5497263000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>5549865000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>5651305000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>5688356000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>5686141000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>5729812000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6252767994.8565</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6275860810.76853</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>6246788020.65491</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>6261408128.90487</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6328953176.89696</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6364898649.35328</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>6419739543.42461</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>6530270237.83842</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6670719886.31428</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>6462196298.34405</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>6497796868.58755</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>6597916680.46395</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>6618082899.76405</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>6605720772.61275</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>6656959460.65489</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3184800428.17491</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3170239217.63259</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3112534304.14413</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3134970650.75014</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3154711696.0629</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3116829277.40687</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3114063986.82157</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>3172134726.08532</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>3232791193.88891</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3120431818.48127</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>3125263078.22587</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>3174199101.61736</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>3157720351.57556</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>3143276612.57288</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>3146869184.22086</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3756460</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3783490</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>3779940</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3804560</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>3828330</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>3873820</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3941430</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4013690</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4090350</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4072620</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>4102240</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>4166000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>4211030</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>4230600</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>4268490</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3245220</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3266550</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3259580</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3276810</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3291560</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3329350</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3385420</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3454200</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3520560</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3496720</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>3527070</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>3591660</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>3642810</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>3664940</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>3696920</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6252767994.8565</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6275860810.76853</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6246788020.65491</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6261408128.90487</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6328953176.89696</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6364898649.35328</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6419739543.42461</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6530270237.83842</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6670719886.31428</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6462196298.34405</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>6497796868.58755</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>6597916680.46395</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>6618082899.76405</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>6605720772.61275</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>6656959460.65489</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>5384854000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5395217000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5368603000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5374061000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5422009000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5448220000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>5489266000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5593980000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5715131000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>5497263000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>5549865000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>5651305000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>5688356000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>5686141000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>5729812000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>334335.25704</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>339350.18392</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>368345.61984</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>454301.68448</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>527502.29007</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>561338.16882</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>608876.97796</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>707979.05725</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>803876.47684</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>725903.85384</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>721151.50203</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>805059.1632</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>764692.78864</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>803041.64145</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>809630.6777</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>175648.30844</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>176084.09512</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>190900.092</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>233417.12464</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>267700.9629</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>279646.06098</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>298435.52816</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>345265.6794</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>383192.37764</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>355343.71136</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>347747.0184</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>382594.8192</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>362178.95296</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>381886.65516</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>389663.9292</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>889234.602817536</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>897358.299078415</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>909308.190928712</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>925373.433586671</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>939492.067935218</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>946038.552087607</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>970165.066182435</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1004140.74449548</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>1036503.38819765</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1057374.17347537</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1071011.08564</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1082555.7303454</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1093477.03335307</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>1106747.30244974</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1124583.16411394</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
